--- a/public/sample-reviews.xlsx
+++ b/public/sample-reviews.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +418,9 @@
       <c r="F1" t="str">
         <v>작성일</v>
       </c>
+      <c r="G1" t="str">
+        <v>리뷰 이미지</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -438,6 +441,9 @@
       <c r="F2" t="str">
         <v>2026-06-14</v>
       </c>
+      <c r="G2" t="str">
+        <v>https://picsum.photos/id/1/600/800</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -458,6 +464,9 @@
       <c r="F3" t="str">
         <v>2026-06-18</v>
       </c>
+      <c r="G3" t="str">
+        <v>https://picsum.photos/id/2/600/800</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -478,6 +487,9 @@
       <c r="F4" t="str">
         <v>2026-06-21</v>
       </c>
+      <c r="G4" t="str">
+        <v>https://picsum.photos/id/3/600/800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -498,6 +510,9 @@
       <c r="F5" t="str">
         <v>2026-06-25</v>
       </c>
+      <c r="G5" t="str">
+        <v>https://picsum.photos/id/4/600/800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -518,6 +533,9 @@
       <c r="F6" t="str">
         <v>2026-07-02</v>
       </c>
+      <c r="G6" t="str">
+        <v>https://picsum.photos/id/5/600/800</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -538,10 +556,13 @@
       <c r="F7" t="str">
         <v>2026-07-09</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>